--- a/实验器材表.xlsx
+++ b/实验器材表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17120"/>
+    <workbookView windowHeight="23860"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
   <si>
     <t>需购买实验器材</t>
   </si>
@@ -56,9 +56,6 @@
     <t>用于接受线圈与偏转线圈</t>
   </si>
   <si>
-    <t>d</t>
-  </si>
-  <si>
     <t>长方体铝合金固定框架</t>
   </si>
   <si>
@@ -189,12 +186,6 @@
   </si>
   <si>
     <t>接收放大后的偏转信息</t>
-  </si>
-  <si>
-    <t>砝码</t>
-  </si>
-  <si>
-    <t>ads芯片</t>
   </si>
 </sst>
 </file>
@@ -1483,269 +1474,251 @@
       <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="3"/>
+      <c r="F3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>11</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>12</v>
       </c>
       <c r="I3" s="11"/>
       <c r="J3" s="11"/>
     </row>
     <row r="4" ht="21" customHeight="1" spans="1:10">
       <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>14</v>
       </c>
       <c r="C4" s="10">
         <f>19*3</f>
         <v>57</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
     </row>
     <row r="5" ht="21" customHeight="1" spans="1:10">
       <c r="A5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="10">
         <v>42.2</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>23</v>
       </c>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
     </row>
     <row r="6" ht="21" customHeight="1" spans="1:10">
       <c r="A6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>25</v>
       </c>
       <c r="C6" s="10">
         <v>8.09</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8" t="s">
+      <c r="G6" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>28</v>
       </c>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
     </row>
     <row r="7" ht="21" customHeight="1" spans="1:10">
       <c r="A7" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="10">
         <v>340</v>
       </c>
       <c r="D7" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>32</v>
       </c>
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
     </row>
     <row r="8" ht="21" customHeight="1" spans="1:10">
       <c r="A8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="C8" s="10">
         <v>19.85</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
     </row>
     <row r="9" ht="21" customHeight="1" spans="1:10">
       <c r="A9" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="10">
         <v>9.82</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="G9" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="11"/>
     </row>
     <row r="10" ht="21" customHeight="1" spans="1:10">
       <c r="A10" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="10">
         <v>4.5</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>9</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="E10" s="3"/>
       <c r="I10" s="11"/>
       <c r="J10" s="11"/>
     </row>
     <row r="11" ht="21" customHeight="1" spans="1:10">
       <c r="A11" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
     </row>
     <row r="12" ht="21" customHeight="1" spans="1:10">
       <c r="A12" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="10">
         <v>25.64</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="E12" s="3"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
     </row>
     <row r="13" ht="21" customHeight="1" spans="1:10">
       <c r="A13" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>49</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>50</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
     </row>
     <row r="14" ht="21" customHeight="1" spans="1:10">
       <c r="A14" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="10">
         <v>350</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>9</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E14" s="11"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
     </row>
@@ -1757,12 +1730,8 @@
       <c r="J15" s="11"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>9</v>
-      </c>
+      <c r="A16" s="12"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
@@ -1773,12 +1742,8 @@
       <c r="J16" s="11"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="A17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="13">
-        <v>1</v>
-      </c>
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
